--- a/Data/Enemy/EnemyPatrolPos.xlsx
+++ b/Data/Enemy/EnemyPatrolPos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\Game\3DGame\Data\Enemy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D74EC8-7617-4CC9-9B6A-7FFD256EBFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA7BBE3-34C0-4F5C-A0C1-C20236FC8AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="5325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,24 +30,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>patrolIndex</t>
+  </si>
+  <si>
     <t>posX</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>posY</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>posZ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>patrolIndex</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -90,8 +85,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -379,156 +377,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>250</v>
+      </c>
+      <c r="D2" s="1">
+        <v>160</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="1">
+        <v>160</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1800</v>
+      </c>
+      <c r="D4" s="1">
+        <v>160</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2650</v>
+      </c>
+      <c r="D5" s="1">
+        <v>160</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+      <c r="C6" s="1">
+        <v>2650</v>
+      </c>
+      <c r="D6" s="1">
+        <v>160</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>250</v>
-      </c>
-      <c r="D2">
-        <v>150</v>
-      </c>
-      <c r="E2">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-      <c r="D3">
-        <v>150</v>
-      </c>
-      <c r="E3">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>150</v>
-      </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>250</v>
-      </c>
-      <c r="D5">
-        <v>150</v>
-      </c>
-      <c r="E5">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
+      <c r="C7" s="1">
+        <v>1250</v>
+      </c>
+      <c r="D7" s="1">
+        <v>160</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>350</v>
-      </c>
-      <c r="D6">
-        <v>150</v>
-      </c>
-      <c r="E6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1250</v>
+      </c>
+      <c r="D8" s="1">
+        <v>160</v>
+      </c>
+      <c r="E8" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>500</v>
-      </c>
-      <c r="D7">
-        <v>150</v>
-      </c>
-      <c r="E7">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>400</v>
-      </c>
-      <c r="D8">
-        <v>150</v>
-      </c>
-      <c r="E8">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9">
-        <v>150</v>
-      </c>
-      <c r="E9">
-        <v>300</v>
+      <c r="C9" s="1">
+        <v>2400</v>
+      </c>
+      <c r="D9" s="1">
+        <v>160</v>
+      </c>
+      <c r="E9" s="1">
+        <v>450</v>
       </c>
     </row>
   </sheetData>
